--- a/bakup/customers/abas.xlsx
+++ b/bakup/customers/abas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="266">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -736,6 +736,87 @@
   </si>
   <si>
     <t>اوسکار</t>
+  </si>
+  <si>
+    <t>1405/06/06</t>
+  </si>
+  <si>
+    <t>سیگار مزه</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>دنگ سوسیس خونه یاسین</t>
+  </si>
+  <si>
+    <t>1405/06/09</t>
+  </si>
+  <si>
+    <t>مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>1405/06/16</t>
+  </si>
+  <si>
+    <t>چیپس ابمیوه</t>
+  </si>
+  <si>
+    <t>1405/06/18</t>
+  </si>
+  <si>
+    <t>الباقی گول</t>
+  </si>
+  <si>
+    <t>1405/06/21</t>
+  </si>
+  <si>
+    <t>بستنی پچ پچ سیگار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دنگ سس </t>
+  </si>
+  <si>
+    <t>1405/07/02</t>
+  </si>
+  <si>
+    <t>پچ پچ</t>
+  </si>
+  <si>
+    <t>1405/07/04</t>
+  </si>
+  <si>
+    <t>سیب موز</t>
+  </si>
+  <si>
+    <t>1405/07/06</t>
+  </si>
+  <si>
+    <t>1405/07/07</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>1405/07/14</t>
+  </si>
+  <si>
+    <t>1404/07/16</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
+  </si>
+  <si>
+    <t>1405/07/19</t>
+  </si>
+  <si>
+    <t>عطر</t>
+  </si>
+  <si>
+    <t>1405/07/21</t>
   </si>
 </sst>
 </file>
@@ -851,7 +932,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1291,8 +1393,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B232</f>
-        <v>3677000</v>
+        <f>B257</f>
+        <v>2730000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4346,165 +4448,503 @@
     <row r="220" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B220" s="8"/>
+        <v>4069000</v>
+      </c>
+      <c r="B220" s="8">
+        <v>392000</v>
+      </c>
       <c r="C220" s="8"/>
-      <c r="D220" s="1"/>
-      <c r="E220" s="1"/>
+      <c r="D220" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="221" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B221" s="8"/>
+        <v>4185000</v>
+      </c>
+      <c r="B221" s="8">
+        <v>116000</v>
+      </c>
       <c r="C221" s="8"/>
-      <c r="D221" s="1"/>
-      <c r="E221" s="1"/>
+      <c r="D221" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="222" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
+        <v>2185000</v>
       </c>
       <c r="B222" s="8"/>
-      <c r="C222" s="8"/>
-      <c r="D222" s="1"/>
+      <c r="C222" s="8">
+        <v>2000000</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="E222" s="1"/>
     </row>
     <row r="223" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B223" s="8"/>
+        <v>2355000</v>
+      </c>
+      <c r="B223" s="8">
+        <v>170000</v>
+      </c>
       <c r="C223" s="8"/>
-      <c r="D223" s="1"/>
-      <c r="E223" s="1"/>
+      <c r="D223" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="224" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B224" s="8"/>
+        <v>2405000</v>
+      </c>
+      <c r="B224" s="8">
+        <v>50000</v>
+      </c>
       <c r="C224" s="8"/>
-      <c r="D224" s="1"/>
+      <c r="D224" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E224" s="1"/>
     </row>
     <row r="225" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B225" s="8"/>
+        <v>2560000</v>
+      </c>
+      <c r="B225" s="8">
+        <v>155000</v>
+      </c>
       <c r="C225" s="8"/>
-      <c r="D225" s="1"/>
-      <c r="E225" s="1"/>
+      <c r="D225" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="226" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B226" s="8"/>
+        <v>2645000</v>
+      </c>
+      <c r="B226" s="8">
+        <v>85000</v>
+      </c>
       <c r="C226" s="8"/>
-      <c r="D226" s="1"/>
-      <c r="E226" s="1"/>
+      <c r="D226" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="227" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B227" s="8"/>
+        <v>2682000</v>
+      </c>
+      <c r="B227" s="8">
+        <v>37000</v>
+      </c>
       <c r="C227" s="8"/>
-      <c r="D227" s="1"/>
-      <c r="E227" s="1"/>
+      <c r="D227" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="228" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B228" s="8"/>
+        <v>2864000</v>
+      </c>
+      <c r="B228" s="8">
+        <v>182000</v>
+      </c>
       <c r="C228" s="8"/>
-      <c r="D228" s="1"/>
-      <c r="E228" s="1"/>
+      <c r="D228" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="229" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <f t="shared" si="9"/>
-        <v>3677000</v>
-      </c>
-      <c r="B229" s="8"/>
+        <v>2960000</v>
+      </c>
+      <c r="B229" s="8">
+        <v>96000</v>
+      </c>
       <c r="C229" s="8"/>
-      <c r="D229" s="1"/>
+      <c r="D229" s="1" t="s">
+        <v>252</v>
+      </c>
       <c r="E229" s="1"/>
     </row>
     <row r="230" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B230" s="9">
         <f>SUM(B210:B229)+B204</f>
-        <v>12875500</v>
+        <v>14158500</v>
       </c>
       <c r="C230" s="9">
         <f>SUM(C210:C229)+C204</f>
-        <v>9198500</v>
+        <v>11198500</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="232" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="10">
         <f>A229</f>
-        <v>3677000</v>
+        <v>2960000</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>198</v>
       </c>
       <c r="D232" s="12"/>
     </row>
-    <row r="233" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B233" t="s">
-        <v>88</v>
-      </c>
-      <c r="D233" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>10</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C233" s="2"/>
+    </row>
+    <row r="234" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A234" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="8">
+        <f>B232+B235-C235</f>
+        <v>3010000</v>
+      </c>
+      <c r="B235" s="8">
+        <v>50000</v>
+      </c>
+      <c r="C235" s="8"/>
+      <c r="D235" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="8">
+        <f>A235+B236-C236</f>
+        <v>3235000</v>
+      </c>
+      <c r="B236" s="8">
+        <v>225000</v>
+      </c>
+      <c r="C236" s="8"/>
+      <c r="D236" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="8">
+        <f t="shared" ref="A237:A254" si="10">A236+B237-C237</f>
+        <v>3285000</v>
+      </c>
+      <c r="B237" s="8">
+        <v>50000</v>
+      </c>
+      <c r="C237" s="8"/>
+      <c r="D237" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E237" s="1"/>
+    </row>
+    <row r="238" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="8">
+        <f t="shared" si="10"/>
+        <v>3205000</v>
+      </c>
+      <c r="B238" s="8"/>
+      <c r="C238" s="8">
+        <v>80000</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="8">
+        <f t="shared" si="10"/>
+        <v>3221000</v>
+      </c>
+      <c r="B239" s="8">
+        <v>16000</v>
+      </c>
+      <c r="C239" s="8"/>
+      <c r="D239" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="8">
+        <f t="shared" si="10"/>
+        <v>3285000</v>
+      </c>
+      <c r="B240" s="8">
+        <v>64000</v>
+      </c>
+      <c r="C240" s="8"/>
+      <c r="D240" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="8">
+        <f t="shared" si="10"/>
+        <v>3485000</v>
+      </c>
+      <c r="B241" s="8">
+        <v>200000</v>
+      </c>
+      <c r="C241" s="8"/>
+      <c r="D241" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E241" s="1"/>
+    </row>
+    <row r="242" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="8">
+        <f t="shared" si="10"/>
+        <v>1985000</v>
+      </c>
+      <c r="B242" s="8"/>
+      <c r="C242" s="8">
+        <v>1500000</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="8">
+        <f t="shared" si="10"/>
+        <v>2025000</v>
+      </c>
+      <c r="B243" s="8">
+        <v>40000</v>
+      </c>
+      <c r="C243" s="8"/>
+      <c r="D243" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="8">
+        <f t="shared" si="10"/>
+        <v>2250000</v>
+      </c>
+      <c r="B244" s="8">
+        <v>225000</v>
+      </c>
+      <c r="C244" s="8"/>
+      <c r="D244" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="8">
+        <f t="shared" si="10"/>
+        <v>2430000</v>
+      </c>
+      <c r="B245" s="8">
+        <v>180000</v>
+      </c>
+      <c r="C245" s="8"/>
+      <c r="D245" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="8">
+        <f t="shared" si="10"/>
+        <v>2730000</v>
+      </c>
+      <c r="B246" s="8">
+        <v>300000</v>
+      </c>
+      <c r="C246" s="8"/>
+      <c r="D246" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="8">
+        <f t="shared" si="10"/>
+        <v>2730000</v>
+      </c>
+      <c r="B247" s="8"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="1"/>
+      <c r="E247" s="1"/>
+    </row>
+    <row r="248" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="8">
+        <f t="shared" si="10"/>
+        <v>2730000</v>
+      </c>
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="1"/>
+      <c r="E248" s="1"/>
+    </row>
+    <row r="249" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="8">
+        <f t="shared" si="10"/>
+        <v>2730000</v>
+      </c>
+      <c r="B249" s="8"/>
+      <c r="C249" s="8"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+    </row>
+    <row r="250" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="8">
+        <f t="shared" si="10"/>
+        <v>2730000</v>
+      </c>
+      <c r="B250" s="8"/>
+      <c r="C250" s="8"/>
+      <c r="D250" s="1"/>
+      <c r="E250" s="1"/>
+    </row>
+    <row r="251" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="8">
+        <f t="shared" si="10"/>
+        <v>2730000</v>
+      </c>
+      <c r="B251" s="8"/>
+      <c r="C251" s="8"/>
+      <c r="D251" s="1"/>
+      <c r="E251" s="1"/>
+    </row>
+    <row r="252" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="8">
+        <f t="shared" si="10"/>
+        <v>2730000</v>
+      </c>
+      <c r="B252" s="8"/>
+      <c r="C252" s="8"/>
+      <c r="D252" s="1"/>
+      <c r="E252" s="1"/>
+    </row>
+    <row r="253" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="8">
+        <f t="shared" si="10"/>
+        <v>2730000</v>
+      </c>
+      <c r="B253" s="8"/>
+      <c r="C253" s="8"/>
+      <c r="D253" s="1"/>
+      <c r="E253" s="1"/>
+    </row>
+    <row r="254" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="8">
+        <f t="shared" si="10"/>
+        <v>2730000</v>
+      </c>
+      <c r="B254" s="8"/>
+      <c r="C254" s="8"/>
+      <c r="D254" s="1"/>
+      <c r="E254" s="1"/>
+    </row>
+    <row r="255" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B255" s="9">
+        <f>SUM(B235:B254)+B230</f>
+        <v>15508500</v>
+      </c>
+      <c r="C255" s="9">
+        <f>SUM(C235:C254)+C230</f>
+        <v>12778500</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B257" s="10">
+        <f>A254</f>
+        <v>2730000</v>
+      </c>
+      <c r="C257" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D257" s="12"/>
+    </row>
+    <row r="258" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C257:D257"/>
     <mergeCell ref="C232:D232"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C128:D128"/>
@@ -4513,17 +4953,28 @@
     <mergeCell ref="C206:D206"/>
   </mergeCells>
   <conditionalFormatting sqref="B102">
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="19" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B128">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B154">
     <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4534,7 +4985,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154">
+  <conditionalFormatting sqref="B180">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4545,7 +4996,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B180">
+  <conditionalFormatting sqref="B206">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4556,7 +5007,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B206">
+  <conditionalFormatting sqref="B232">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4567,7 +5018,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B232">
+  <conditionalFormatting sqref="B257">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
